--- a/preproc/prolific/Corpus_fq.xlsx
+++ b/preproc/prolific/Corpus_fq.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28730"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin\Documents\R\WebEye\preproc\prolific\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF378AAF-E00F-469E-AB8B-194CD4F19BCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AC162EE-7B9F-4F9C-A0BE-BA720618BC1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Frequency" sheetId="1" r:id="rId1"/>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1256" uniqueCount="618">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1257" uniqueCount="618">
   <si>
     <t>Sentence</t>
   </si>
@@ -14864,1279 +14864,1402 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FEEEAAE-8BB8-47FE-9AE6-FF09D2334048}">
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:J41"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="3" max="3" width="28.90625" customWidth="1"/>
-    <col min="6" max="6" width="47" customWidth="1"/>
+    <col min="4" max="4" width="28.90625" customWidth="1"/>
+    <col min="7" max="7" width="47" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" s="9" t="s">
+        <v>252</v>
+      </c>
+      <c r="B1" s="9" t="s">
         <v>332</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="C1" s="8" t="s">
         <v>334</v>
       </c>
-      <c r="C1" s="8" t="s">
-        <v>0</v>
-      </c>
       <c r="D1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="8" t="s">
         <v>380</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="F1" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="G1" s="9" t="s">
         <v>209</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="H1" s="9" t="s">
         <v>337</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="I1" s="9" t="s">
         <v>367</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="J1" s="9" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A2" s="5">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="5">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
         <v>335</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>333</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>381</v>
       </c>
-      <c r="E2">
-        <f>LEN(C2)</f>
+      <c r="F2">
+        <f>LEN(D2)</f>
         <v>19</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="G2" s="5" t="s">
         <v>346</v>
       </c>
-      <c r="G2" s="5">
-        <v>0</v>
-      </c>
       <c r="H2" s="5">
-        <f>IF(ISBLANK(C2),0,LEN(TRIM(C2))-LEN(SUBSTITUTE(C2," ",""))+1)</f>
+        <v>0</v>
+      </c>
+      <c r="I2" s="5">
+        <f>IF(ISBLANK(D2),0,LEN(TRIM(D2))-LEN(SUBSTITUTE(D2," ",""))+1)</f>
         <v>5</v>
       </c>
-      <c r="I2" s="5">
+      <c r="J2" s="5">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A3" s="5">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>21</v>
+      </c>
+      <c r="B3" s="5">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>335</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>339</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>390</v>
       </c>
-      <c r="E3">
-        <f>LEN(C3)</f>
+      <c r="F3">
+        <f>LEN(D3)</f>
         <v>21</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="G3" s="5" t="s">
         <v>349</v>
       </c>
-      <c r="G3" s="5">
-        <v>0</v>
-      </c>
       <c r="H3" s="5">
-        <f t="shared" ref="H3:H36" si="0">IF(ISBLANK(C3),0,LEN(TRIM(C3))-LEN(SUBSTITUTE(C3," ",""))+1)</f>
+        <v>0</v>
+      </c>
+      <c r="I3" s="5">
+        <f t="shared" ref="I3:I36" si="0">IF(ISBLANK(D3),0,LEN(TRIM(D3))-LEN(SUBSTITUTE(D3," ",""))+1)</f>
         <v>5</v>
       </c>
-      <c r="I3" s="5">
+      <c r="J3" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A4" s="5">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" s="5">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>335</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>341</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>382</v>
       </c>
-      <c r="E4">
-        <f>LEN(C4)</f>
+      <c r="F4">
+        <f>LEN(D4)</f>
         <v>21</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="G4" s="5" t="s">
         <v>347</v>
       </c>
-      <c r="G4" s="5">
-        <v>1</v>
-      </c>
       <c r="H4" s="5">
+        <v>1</v>
+      </c>
+      <c r="I4" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="I4" s="5">
+      <c r="J4" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A5" s="5">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>22</v>
+      </c>
+      <c r="B5" s="5">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>335</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>342</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>383</v>
       </c>
-      <c r="E5">
-        <f t="shared" ref="E5:E36" si="1">LEN(C5)</f>
+      <c r="F5">
+        <f t="shared" ref="F5:F36" si="1">LEN(D5)</f>
         <v>20</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="G5" s="5" t="s">
         <v>350</v>
       </c>
-      <c r="G5" s="5">
-        <v>1</v>
-      </c>
       <c r="H5" s="5">
+        <v>1</v>
+      </c>
+      <c r="I5" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="I5" s="5">
+      <c r="J5" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A6" s="5">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>3</v>
+      </c>
+      <c r="B6" s="5">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>335</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>344</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>384</v>
       </c>
-      <c r="E6">
+      <c r="F6">
         <f t="shared" si="1"/>
         <v>19</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="G6" s="5" t="s">
         <v>348</v>
       </c>
-      <c r="G6" s="5">
-        <v>0</v>
-      </c>
       <c r="H6" s="5">
+        <v>0</v>
+      </c>
+      <c r="I6" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="I6" s="5">
+      <c r="J6" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A7" s="5">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>23</v>
+      </c>
+      <c r="B7" s="5">
         <v>6</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>335</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>351</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>385</v>
       </c>
-      <c r="E7">
+      <c r="F7">
         <f t="shared" si="1"/>
         <v>21</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="G7" s="5" t="s">
         <v>352</v>
       </c>
-      <c r="G7" s="5">
-        <v>1</v>
-      </c>
       <c r="H7" s="5">
+        <v>1</v>
+      </c>
+      <c r="I7" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="I7" s="5">
+      <c r="J7" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A8" s="5">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>4</v>
+      </c>
+      <c r="B8" s="5">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>335</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>355</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>386</v>
       </c>
-      <c r="E8">
+      <c r="F8">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="G8" s="5" t="s">
         <v>356</v>
       </c>
-      <c r="G8" s="5">
-        <v>1</v>
-      </c>
       <c r="H8" s="5">
+        <v>1</v>
+      </c>
+      <c r="I8" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="I8" s="5">
+      <c r="J8" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A9" s="5">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>24</v>
+      </c>
+      <c r="B9" s="5">
         <v>8</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>335</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>358</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>387</v>
       </c>
-      <c r="E9">
+      <c r="F9">
         <f t="shared" si="1"/>
         <v>19</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="G9" s="5" t="s">
         <v>360</v>
       </c>
-      <c r="G9" s="5">
-        <v>1</v>
-      </c>
       <c r="H9" s="5">
+        <v>1</v>
+      </c>
+      <c r="I9" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="I9" s="5">
+      <c r="J9" s="5">
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A10" s="5">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>5</v>
+      </c>
+      <c r="B10" s="5">
         <v>9</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>335</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>361</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>53</v>
       </c>
-      <c r="E10">
+      <c r="F10">
         <f t="shared" si="1"/>
         <v>21</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="G10" s="5" t="s">
         <v>363</v>
       </c>
-      <c r="G10" s="5">
-        <v>1</v>
-      </c>
       <c r="H10" s="5">
+        <v>1</v>
+      </c>
+      <c r="I10" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="I10" s="5">
+      <c r="J10" s="5">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A11" s="5">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>25</v>
+      </c>
+      <c r="B11" s="5">
         <v>10</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>335</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>364</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>388</v>
       </c>
-      <c r="E11">
+      <c r="F11">
         <f t="shared" si="1"/>
         <v>21</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="G11" s="5" t="s">
         <v>365</v>
       </c>
-      <c r="G11" s="5">
-        <v>0</v>
-      </c>
       <c r="H11" s="5">
+        <v>0</v>
+      </c>
+      <c r="I11" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="I11" s="5">
+      <c r="J11" s="5">
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A12" s="5">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>6</v>
+      </c>
+      <c r="B12" s="5">
         <v>11</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>335</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>369</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>391</v>
       </c>
-      <c r="E12">
+      <c r="F12">
         <f t="shared" si="1"/>
         <v>21</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="G12" s="5" t="s">
         <v>371</v>
       </c>
-      <c r="G12" s="5">
-        <v>0</v>
-      </c>
       <c r="H12" s="5">
+        <v>0</v>
+      </c>
+      <c r="I12" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="I12" s="5">
+      <c r="J12" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A13" s="5">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>26</v>
+      </c>
+      <c r="B13" s="5">
         <v>12</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>335</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>372</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>389</v>
       </c>
-      <c r="E13">
+      <c r="F13">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="G13" s="5" t="s">
         <v>398</v>
       </c>
-      <c r="G13" s="5">
-        <v>1</v>
-      </c>
       <c r="H13" s="5">
+        <v>1</v>
+      </c>
+      <c r="I13" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="I13" s="5">
+      <c r="J13" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A14" s="5">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>7</v>
+      </c>
+      <c r="B14" s="5">
         <v>13</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
         <v>335</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>374</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>392</v>
       </c>
-      <c r="E14">
+      <c r="F14">
         <f t="shared" si="1"/>
         <v>21</v>
       </c>
-      <c r="F14" s="5" t="s">
+      <c r="G14" s="5" t="s">
         <v>375</v>
       </c>
-      <c r="G14" s="5">
-        <v>1</v>
-      </c>
       <c r="H14" s="5">
+        <v>1</v>
+      </c>
+      <c r="I14" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="I14" s="5">
+      <c r="J14" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A15" s="5">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>27</v>
+      </c>
+      <c r="B15" s="5">
         <v>14</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
         <v>335</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
         <v>377</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>393</v>
       </c>
-      <c r="E15">
+      <c r="F15">
         <f t="shared" si="1"/>
         <v>19</v>
       </c>
-      <c r="F15" s="5" t="s">
+      <c r="G15" s="5" t="s">
         <v>379</v>
       </c>
-      <c r="G15" s="5">
-        <v>0</v>
-      </c>
       <c r="H15" s="5">
+        <v>0</v>
+      </c>
+      <c r="I15" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="I15" s="5">
+      <c r="J15" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A16" s="5">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>8</v>
+      </c>
+      <c r="B16" s="5">
         <v>15</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>335</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
         <v>394</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>395</v>
       </c>
-      <c r="E16">
+      <c r="F16">
         <f t="shared" si="1"/>
         <v>21</v>
       </c>
-      <c r="F16" s="5" t="s">
+      <c r="G16" s="5" t="s">
         <v>397</v>
       </c>
-      <c r="G16" s="5">
-        <v>0</v>
-      </c>
       <c r="H16" s="5">
+        <v>0</v>
+      </c>
+      <c r="I16" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="I16" s="5">
+      <c r="J16" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A17" s="5">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>28</v>
+      </c>
+      <c r="B17" s="5">
         <v>16</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
         <v>335</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
         <v>399</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>400</v>
       </c>
-      <c r="E17">
+      <c r="F17">
         <f t="shared" si="1"/>
         <v>19</v>
       </c>
-      <c r="F17" s="5" t="s">
+      <c r="G17" s="5" t="s">
         <v>402</v>
       </c>
-      <c r="G17" s="5">
-        <v>1</v>
-      </c>
       <c r="H17" s="5">
+        <v>1</v>
+      </c>
+      <c r="I17" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="I17" s="5">
+      <c r="J17" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A18" s="5">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>9</v>
+      </c>
+      <c r="B18" s="5">
         <v>17</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
         <v>335</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
         <v>403</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>404</v>
       </c>
-      <c r="E18">
+      <c r="F18">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="F18" s="5" t="s">
+      <c r="G18" s="5" t="s">
         <v>406</v>
       </c>
-      <c r="G18" s="5">
-        <v>0</v>
-      </c>
       <c r="H18" s="5">
+        <v>0</v>
+      </c>
+      <c r="I18" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="I18" s="5">
+      <c r="J18" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A19" s="5">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>29</v>
+      </c>
+      <c r="B19" s="5">
         <v>18</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
         <v>335</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
         <v>407</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
         <v>408</v>
       </c>
-      <c r="E19">
+      <c r="F19">
         <f t="shared" si="1"/>
         <v>21</v>
       </c>
-      <c r="F19" s="5" t="s">
+      <c r="G19" s="5" t="s">
         <v>409</v>
       </c>
-      <c r="G19" s="5">
-        <v>0</v>
-      </c>
       <c r="H19" s="5">
+        <v>0</v>
+      </c>
+      <c r="I19" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="I19" s="5">
+      <c r="J19" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A20" s="5">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>10</v>
+      </c>
+      <c r="B20" s="5">
         <v>19</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
         <v>335</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" t="s">
         <v>411</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>412</v>
       </c>
-      <c r="E20">
+      <c r="F20">
         <f t="shared" si="1"/>
         <v>19</v>
       </c>
-      <c r="F20" s="5" t="s">
+      <c r="G20" s="5" t="s">
         <v>413</v>
       </c>
-      <c r="G20" s="5">
-        <v>0</v>
-      </c>
       <c r="H20" s="5">
+        <v>0</v>
+      </c>
+      <c r="I20" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="I20" s="5">
+      <c r="J20" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A21" s="5">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>30</v>
+      </c>
+      <c r="B21" s="5">
         <v>20</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
         <v>335</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
         <v>414</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" t="s">
         <v>415</v>
       </c>
-      <c r="E21">
+      <c r="F21">
         <f t="shared" si="1"/>
         <v>19</v>
       </c>
-      <c r="F21" s="5" t="s">
+      <c r="G21" s="5" t="s">
         <v>416</v>
       </c>
-      <c r="G21" s="5">
-        <v>1</v>
-      </c>
       <c r="H21" s="5">
+        <v>1</v>
+      </c>
+      <c r="I21" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="I21" s="5">
+      <c r="J21" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A22" s="5">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>11</v>
+      </c>
+      <c r="B22" s="5">
         <v>21</v>
       </c>
-      <c r="B22" t="s">
+      <c r="C22" t="s">
         <v>335</v>
       </c>
-      <c r="C22" t="s">
+      <c r="D22" t="s">
         <v>418</v>
       </c>
-      <c r="D22" t="s">
+      <c r="E22" t="s">
         <v>419</v>
       </c>
-      <c r="E22">
+      <c r="F22">
         <f t="shared" si="1"/>
         <v>21</v>
       </c>
-      <c r="F22" s="5" t="s">
+      <c r="G22" s="5" t="s">
         <v>420</v>
       </c>
-      <c r="G22" s="5">
-        <v>0</v>
-      </c>
       <c r="H22" s="5">
+        <v>0</v>
+      </c>
+      <c r="I22" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="I22" s="5">
+      <c r="J22" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A23" s="5">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>31</v>
+      </c>
+      <c r="B23" s="5">
         <v>22</v>
       </c>
-      <c r="B23" t="s">
+      <c r="C23" t="s">
         <v>335</v>
       </c>
-      <c r="C23" t="s">
+      <c r="D23" t="s">
         <v>421</v>
       </c>
-      <c r="D23" t="s">
+      <c r="E23" t="s">
         <v>422</v>
       </c>
-      <c r="E23">
+      <c r="F23">
         <f t="shared" si="1"/>
         <v>19</v>
       </c>
-      <c r="F23" s="5" t="s">
+      <c r="G23" s="5" t="s">
         <v>423</v>
       </c>
-      <c r="G23" s="5">
-        <v>1</v>
-      </c>
       <c r="H23" s="5">
+        <v>1</v>
+      </c>
+      <c r="I23" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="I23" s="5">
+      <c r="J23" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A24" s="5">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>12</v>
+      </c>
+      <c r="B24" s="5">
         <v>23</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C24" t="s">
         <v>335</v>
       </c>
-      <c r="C24" t="s">
+      <c r="D24" t="s">
         <v>424</v>
       </c>
-      <c r="D24" t="s">
+      <c r="E24" t="s">
         <v>425</v>
       </c>
-      <c r="E24">
+      <c r="F24">
         <f t="shared" si="1"/>
         <v>21</v>
       </c>
-      <c r="F24" s="5" t="s">
+      <c r="G24" s="5" t="s">
         <v>495</v>
       </c>
-      <c r="G24" s="5">
-        <v>0</v>
-      </c>
       <c r="H24" s="5">
+        <v>0</v>
+      </c>
+      <c r="I24" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="I24" s="5">
+      <c r="J24" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A25" s="5">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A25">
+        <v>32</v>
+      </c>
+      <c r="B25" s="5">
         <v>24</v>
       </c>
-      <c r="B25" t="s">
+      <c r="C25" t="s">
         <v>335</v>
       </c>
-      <c r="C25" t="s">
+      <c r="D25" t="s">
         <v>426</v>
       </c>
-      <c r="D25" t="s">
+      <c r="E25" t="s">
         <v>395</v>
       </c>
-      <c r="E25">
+      <c r="F25">
         <f t="shared" si="1"/>
         <v>21</v>
       </c>
-      <c r="F25" s="5" t="s">
+      <c r="G25" s="5" t="s">
         <v>427</v>
       </c>
-      <c r="G25" s="5">
-        <v>1</v>
-      </c>
       <c r="H25" s="5">
+        <v>1</v>
+      </c>
+      <c r="I25" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="I25" s="5">
+      <c r="J25" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A26" s="5">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>13</v>
+      </c>
+      <c r="B26" s="5">
         <v>25</v>
       </c>
-      <c r="B26" t="s">
+      <c r="C26" t="s">
         <v>335</v>
       </c>
-      <c r="C26" t="s">
+      <c r="D26" t="s">
         <v>428</v>
       </c>
-      <c r="D26" t="s">
+      <c r="E26" t="s">
         <v>429</v>
       </c>
-      <c r="E26">
+      <c r="F26">
         <f t="shared" si="1"/>
         <v>21</v>
       </c>
-      <c r="F26" s="5" t="s">
+      <c r="G26" s="5" t="s">
         <v>430</v>
       </c>
-      <c r="G26" s="5">
-        <v>0</v>
-      </c>
       <c r="H26" s="5">
+        <v>0</v>
+      </c>
+      <c r="I26" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="I26" s="5">
+      <c r="J26" s="5">
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A27" s="5">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <v>33</v>
+      </c>
+      <c r="B27" s="5">
         <v>26</v>
       </c>
-      <c r="B27" t="s">
+      <c r="C27" t="s">
         <v>335</v>
       </c>
-      <c r="C27" t="s">
+      <c r="D27" t="s">
         <v>437</v>
       </c>
-      <c r="D27" t="s">
+      <c r="E27" t="s">
         <v>438</v>
       </c>
-      <c r="E27">
+      <c r="F27">
         <f t="shared" si="1"/>
         <v>21</v>
       </c>
-      <c r="F27" s="5" t="s">
+      <c r="G27" s="5" t="s">
         <v>439</v>
       </c>
-      <c r="G27" s="5">
-        <v>1</v>
-      </c>
       <c r="H27" s="5">
+        <v>1</v>
+      </c>
+      <c r="I27" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="I27" s="5">
+      <c r="J27" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A28" s="5">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A28">
+        <v>14</v>
+      </c>
+      <c r="B28" s="5">
         <v>27</v>
       </c>
-      <c r="B28" t="s">
+      <c r="C28" t="s">
         <v>335</v>
       </c>
-      <c r="C28" t="s">
+      <c r="D28" t="s">
         <v>440</v>
       </c>
-      <c r="D28" t="s">
+      <c r="E28" t="s">
         <v>441</v>
       </c>
-      <c r="E28">
+      <c r="F28">
         <f t="shared" si="1"/>
         <v>21</v>
       </c>
-      <c r="F28" s="5" t="s">
+      <c r="G28" s="5" t="s">
         <v>444</v>
       </c>
-      <c r="G28" s="5">
-        <v>1</v>
-      </c>
       <c r="H28" s="5">
+        <v>1</v>
+      </c>
+      <c r="I28" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="I28" s="5">
+      <c r="J28" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A29" s="5">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A29">
+        <v>34</v>
+      </c>
+      <c r="B29" s="5">
         <v>28</v>
       </c>
-      <c r="B29" t="s">
+      <c r="C29" t="s">
         <v>335</v>
       </c>
-      <c r="C29" t="s">
+      <c r="D29" t="s">
         <v>445</v>
       </c>
-      <c r="D29" t="s">
+      <c r="E29" t="s">
         <v>446</v>
       </c>
-      <c r="E29">
+      <c r="F29">
         <f t="shared" si="1"/>
         <v>21</v>
       </c>
-      <c r="F29" s="5" t="s">
+      <c r="G29" s="5" t="s">
         <v>448</v>
       </c>
-      <c r="G29" s="5">
-        <v>1</v>
-      </c>
       <c r="H29" s="5">
+        <v>1</v>
+      </c>
+      <c r="I29" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="I29" s="5">
+      <c r="J29" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A30" s="5">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A30">
+        <v>15</v>
+      </c>
+      <c r="B30" s="5">
         <v>29</v>
       </c>
-      <c r="B30" t="s">
+      <c r="C30" t="s">
         <v>335</v>
       </c>
-      <c r="C30" t="s">
+      <c r="D30" t="s">
         <v>449</v>
       </c>
-      <c r="D30" t="s">
+      <c r="E30" t="s">
         <v>450</v>
       </c>
-      <c r="E30">
+      <c r="F30">
         <f t="shared" si="1"/>
         <v>21</v>
       </c>
-      <c r="F30" s="5" t="s">
+      <c r="G30" s="5" t="s">
         <v>451</v>
       </c>
-      <c r="G30" s="5">
-        <v>0</v>
-      </c>
       <c r="H30" s="5">
+        <v>0</v>
+      </c>
+      <c r="I30" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="I30" s="5">
+      <c r="J30" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A31" s="5">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A31">
+        <v>35</v>
+      </c>
+      <c r="B31" s="5">
         <v>30</v>
       </c>
-      <c r="B31" t="s">
+      <c r="C31" t="s">
         <v>335</v>
       </c>
-      <c r="C31" t="s">
+      <c r="D31" t="s">
         <v>453</v>
       </c>
-      <c r="D31" t="s">
+      <c r="E31" t="s">
         <v>61</v>
       </c>
-      <c r="E31">
+      <c r="F31">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="F31" s="5" t="s">
+      <c r="G31" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="G31" s="5">
-        <v>0</v>
-      </c>
       <c r="H31" s="5">
+        <v>0</v>
+      </c>
+      <c r="I31" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="I31" s="5">
+      <c r="J31" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A32" s="5">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A32">
+        <v>16</v>
+      </c>
+      <c r="B32" s="5">
         <v>31</v>
       </c>
-      <c r="B32" t="s">
+      <c r="C32" t="s">
         <v>335</v>
       </c>
-      <c r="C32" t="s">
+      <c r="D32" t="s">
         <v>455</v>
       </c>
-      <c r="D32" t="s">
+      <c r="E32" t="s">
         <v>456</v>
       </c>
-      <c r="E32">
+      <c r="F32">
         <f t="shared" si="1"/>
         <v>21</v>
       </c>
-      <c r="F32" s="5" t="s">
+      <c r="G32" s="5" t="s">
         <v>457</v>
       </c>
-      <c r="G32" s="5">
-        <v>1</v>
-      </c>
       <c r="H32" s="5">
+        <v>1</v>
+      </c>
+      <c r="I32" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="I32" s="5">
+      <c r="J32" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A33" s="5">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A33">
+        <v>36</v>
+      </c>
+      <c r="B33" s="5">
         <v>32</v>
       </c>
-      <c r="B33" t="s">
+      <c r="C33" t="s">
         <v>335</v>
       </c>
-      <c r="C33" t="s">
+      <c r="D33" t="s">
         <v>458</v>
       </c>
-      <c r="D33" t="s">
+      <c r="E33" t="s">
         <v>459</v>
       </c>
-      <c r="E33">
+      <c r="F33">
         <f t="shared" si="1"/>
         <v>21</v>
       </c>
-      <c r="F33" s="5" t="s">
+      <c r="G33" s="5" t="s">
         <v>460</v>
       </c>
-      <c r="G33" s="5">
-        <v>1</v>
-      </c>
       <c r="H33" s="5">
+        <v>1</v>
+      </c>
+      <c r="I33" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="I33" s="5">
+      <c r="J33" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A34" s="5">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A34">
+        <v>17</v>
+      </c>
+      <c r="B34" s="5">
         <v>33</v>
       </c>
-      <c r="B34" t="s">
+      <c r="C34" t="s">
         <v>335</v>
       </c>
-      <c r="C34" t="s">
+      <c r="D34" t="s">
         <v>467</v>
       </c>
-      <c r="D34" t="s">
+      <c r="E34" t="s">
         <v>462</v>
       </c>
-      <c r="E34">
+      <c r="F34">
         <f t="shared" si="1"/>
         <v>21</v>
       </c>
-      <c r="F34" s="5" t="s">
+      <c r="G34" s="5" t="s">
         <v>463</v>
       </c>
-      <c r="G34" s="5">
-        <v>0</v>
-      </c>
       <c r="H34" s="5">
+        <v>0</v>
+      </c>
+      <c r="I34" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="I34" s="5">
+      <c r="J34" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A35" s="5">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A35">
+        <v>37</v>
+      </c>
+      <c r="B35" s="5">
         <v>34</v>
       </c>
-      <c r="B35" t="s">
+      <c r="C35" t="s">
         <v>335</v>
       </c>
-      <c r="C35" t="s">
+      <c r="D35" t="s">
         <v>464</v>
       </c>
-      <c r="D35" t="s">
+      <c r="E35" t="s">
         <v>465</v>
       </c>
-      <c r="E35">
+      <c r="F35">
         <f t="shared" si="1"/>
         <v>19</v>
       </c>
-      <c r="F35" s="5" t="s">
+      <c r="G35" s="5" t="s">
         <v>466</v>
       </c>
-      <c r="G35" s="5">
-        <v>1</v>
-      </c>
       <c r="H35" s="5">
+        <v>1</v>
+      </c>
+      <c r="I35" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="I35" s="5">
+      <c r="J35" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A36" s="5">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A36">
+        <v>18</v>
+      </c>
+      <c r="B36" s="5">
         <v>35</v>
       </c>
-      <c r="B36" t="s">
+      <c r="C36" t="s">
         <v>335</v>
       </c>
-      <c r="C36" t="s">
+      <c r="D36" t="s">
         <v>472</v>
       </c>
-      <c r="D36" t="s">
+      <c r="E36" t="s">
         <v>473</v>
       </c>
-      <c r="E36">
+      <c r="F36">
         <f t="shared" si="1"/>
         <v>19</v>
       </c>
-      <c r="F36" s="5" t="s">
+      <c r="G36" s="5" t="s">
         <v>474</v>
       </c>
-      <c r="G36" s="5">
-        <v>1</v>
-      </c>
       <c r="H36" s="5">
+        <v>1</v>
+      </c>
+      <c r="I36" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="I36" s="5">
+      <c r="J36" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A37" s="5">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A37">
+        <v>38</v>
+      </c>
+      <c r="B37" s="5">
         <v>36</v>
       </c>
-      <c r="B37" t="s">
+      <c r="C37" t="s">
         <v>335</v>
       </c>
-      <c r="C37" t="s">
+      <c r="D37" t="s">
         <v>478</v>
       </c>
-      <c r="D37" t="s">
+      <c r="E37" t="s">
         <v>479</v>
       </c>
-      <c r="E37">
-        <f t="shared" ref="E37:E41" si="2">LEN(C37)</f>
+      <c r="F37">
+        <f t="shared" ref="F37:F41" si="2">LEN(D37)</f>
         <v>21</v>
       </c>
-      <c r="F37" s="5" t="s">
+      <c r="G37" s="5" t="s">
         <v>481</v>
       </c>
-      <c r="G37" s="5">
-        <v>0</v>
-      </c>
       <c r="H37" s="5">
-        <f t="shared" ref="H37:H41" si="3">IF(ISBLANK(C37),0,LEN(TRIM(C37))-LEN(SUBSTITUTE(C37," ",""))+1)</f>
+        <v>0</v>
+      </c>
+      <c r="I37" s="5">
+        <f t="shared" ref="I37:I41" si="3">IF(ISBLANK(D37),0,LEN(TRIM(D37))-LEN(SUBSTITUTE(D37," ",""))+1)</f>
         <v>4</v>
       </c>
-      <c r="I37" s="5">
+      <c r="J37" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A38" s="5">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A38">
+        <v>19</v>
+      </c>
+      <c r="B38" s="5">
         <v>37</v>
       </c>
-      <c r="B38" t="s">
+      <c r="C38" t="s">
         <v>335</v>
       </c>
-      <c r="C38" t="s">
+      <c r="D38" t="s">
         <v>476</v>
       </c>
-      <c r="D38" t="s">
+      <c r="E38" t="s">
         <v>482</v>
       </c>
-      <c r="E38">
+      <c r="F38">
         <f t="shared" si="2"/>
         <v>20</v>
       </c>
-      <c r="F38" s="5" t="s">
+      <c r="G38" s="5" t="s">
         <v>477</v>
       </c>
-      <c r="G38" s="5">
-        <v>0</v>
-      </c>
       <c r="H38" s="5">
+        <v>0</v>
+      </c>
+      <c r="I38" s="5">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="I38" s="5">
+      <c r="J38" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A39" s="5">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A39">
+        <v>39</v>
+      </c>
+      <c r="B39" s="5">
         <v>38</v>
       </c>
-      <c r="B39" t="s">
+      <c r="C39" t="s">
         <v>335</v>
       </c>
-      <c r="C39" t="s">
+      <c r="D39" t="s">
         <v>483</v>
       </c>
-      <c r="D39" t="s">
+      <c r="E39" t="s">
         <v>484</v>
       </c>
-      <c r="E39">
+      <c r="F39">
         <f t="shared" si="2"/>
         <v>21</v>
       </c>
-      <c r="F39" s="5" t="s">
+      <c r="G39" s="5" t="s">
         <v>485</v>
       </c>
-      <c r="G39" s="5">
-        <v>0</v>
-      </c>
       <c r="H39" s="5">
+        <v>0</v>
+      </c>
+      <c r="I39" s="5">
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
-      <c r="I39" s="5">
+      <c r="J39" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A40" s="5">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A40">
+        <v>20</v>
+      </c>
+      <c r="B40" s="5">
         <v>39</v>
       </c>
-      <c r="B40" t="s">
+      <c r="C40" t="s">
         <v>335</v>
       </c>
-      <c r="C40" t="s">
+      <c r="D40" t="s">
         <v>486</v>
       </c>
-      <c r="D40" t="s">
+      <c r="E40" t="s">
         <v>487</v>
       </c>
-      <c r="E40">
+      <c r="F40">
         <f t="shared" si="2"/>
         <v>21</v>
       </c>
-      <c r="F40" s="5" t="s">
+      <c r="G40" s="5" t="s">
         <v>488</v>
       </c>
-      <c r="G40" s="5">
-        <v>0</v>
-      </c>
       <c r="H40" s="5">
+        <v>0</v>
+      </c>
+      <c r="I40" s="5">
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
-      <c r="I40" s="5">
+      <c r="J40" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A41" s="5">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A41">
         <v>40</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41" s="5">
+        <v>40</v>
+      </c>
+      <c r="C41" t="s">
         <v>335</v>
       </c>
-      <c r="C41" t="s">
+      <c r="D41" t="s">
         <v>489</v>
       </c>
-      <c r="D41" t="s">
+      <c r="E41" t="s">
         <v>490</v>
       </c>
-      <c r="E41">
+      <c r="F41">
         <f t="shared" si="2"/>
         <v>21</v>
       </c>
-      <c r="F41" s="5" t="s">
+      <c r="G41" s="5" t="s">
         <v>491</v>
       </c>
-      <c r="G41" s="5">
-        <v>1</v>
-      </c>
       <c r="H41" s="5">
+        <v>1</v>
+      </c>
+      <c r="I41" s="5">
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
-      <c r="I41" s="5">
+      <c r="J41" s="5">
         <v>3</v>
       </c>
     </row>
